--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 68815-2021 artfynd.xlsx
+++ b/artfynd/A 68815-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137005443</v>
       </c>
       <c r="B2" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137005444</v>
       </c>
       <c r="B3" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137005426</v>
       </c>
       <c r="B4" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137005427</v>
       </c>
       <c r="B5" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
